--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Software Engineer III - Databricks / IAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Gemini, Azure ML, Data Lake, MLflow, FastAPI, Docker, Kubernetes, AKS</t>
+          <t>RAG, S3, Glue, Data Lake, Kinesis, CI/CD, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist – Retail Analytics</t>
+          <t>Software Engineer III - Full Stack Generative AI/LLM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, AWS SageMaker, GCP Vertex AI, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04097c7daf3bc01b</t>
+          <t>https://www.indeed.com/viewjob?jk=70feb696707eb033</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>.Net Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>IT Delight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=68bc0f875eadb538</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Intern AI Engineer - CPU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Home Care Pulse LLC</t>
+          <t>Arm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, AKS, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffa40a281169ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e429da3aa9d3c661</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>AI Fleet Management Solutions</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=2908fc6b24361cd9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Analytics Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>Merge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Redshift, Git, Redshift, PostgreSQL, Tableau, Matplotlib, Python</t>
+          <t>RAG, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,217 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c2f99d5aed6fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>JAVA Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=543ba067914044cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer (Data Science &amp; Automation)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Envita Solutions</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ba6f1c7e5b0ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CAMP Facility Services</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, MongoDB, NoSQL, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer, Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DataVisor</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e354f9573c3496</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52cfb5c52e1363f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Clearwater Analytics (CWAN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Glue, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56b7e33642e1d112</t>
+          <t>https://www.indeed.com/viewjob?jk=759da2a381963696</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks / IAM</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Data Lake, Kinesis, CI/CD, Terraform, Git, Databricks, Kafka</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, S3, Glue, Athena, Data Lake, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Generative AI/LLM</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70feb696707eb033</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdf832082970615</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>.Net Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IT Delight</t>
+          <t>XCEL ENGINEERING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68bc0f875eadb538</t>
+          <t>https://www.indeed.com/viewjob?jk=4231d4a3aa52a2cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intern AI Engineer - CPU</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, AKS, Git, Python, R</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,742 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e429da3aa9d3c661</t>
+          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Fleet Management Solutions</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2908fc6b24361cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=463d640b5be3248c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Merge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf7b7887062295c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SoundThinking</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Copilot, S3, Docker, CI/CD, Jenkins, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Data Lake, Git, Snowflake, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Kinesis, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TomorrowNow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3ff4bbfbd42705c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85b06c3d32383cd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, CI/CD, Git, Kafka, MongoDB, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, FastAPI, Kubernetes, BigQuery, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456a08259c201597</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Cloud IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Cloud IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist V – Ranking &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>itD Tech</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5629128dd200bee0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Science Analyst II - DTP Enterprise Data &amp; Analytics - Digital and Technology Partners - Hybrid/Onsite</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Git, Databricks, PySpark, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c73ca7788ffdf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Support Engineer (North America)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b9404943bd363f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Support Engineer (North America)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=759da2a381963696</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8b44a94d560557d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Industrial AI &amp; Data Engineer (H/F)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vicat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Kafka, Hadoop, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef46044606bc80da</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Prompt Engineering, S3, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fedf9e582c7c5a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Google Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7ff7bbafc6e541</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Databricks, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=159c1652cc5c9d1b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, S3, Glue, Athena, Data Lake, Kubernetes</t>
+          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, FastAPI, Kubernetes, CI/CD, Jenkins, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdf832082970615</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XCEL ENGINEERING</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4231d4a3aa52a2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Python, R</t>
+          <t>RAG, Redshift, CI/CD, Git, Snowflake, Redshift, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>AI Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463d640b5be3248c</t>
+          <t>https://www.indeed.com/viewjob?jk=74f692b1dac1269e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf7b7887062295c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, CI/CD, Jenkins, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=647c0383e2507f57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Data Lake, Git, Snowflake, Databricks, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,602 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Glue, Kinesis, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TomorrowNow</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ff4bbfbd42705c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85b06c3d32383cd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kinesis, CI/CD, Git, Kafka, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, BigQuery, FastAPI, Kubernetes, BigQuery, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=456a08259c201597</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Cloud IAM Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Cloud IAM Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist V – Ranking &amp; Machine Learning</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>itD Tech</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5629128dd200bee0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Science Analyst II - DTP Enterprise Data &amp; Analytics - Digital and Technology Partners - Hybrid/Onsite</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mount Sinai Health System</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Databricks, PySpark, Tableau, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c73ca7788ffdf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Support Engineer (North America)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>n8n</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9404943bd363f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Support Engineer (North America)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>n8n</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44a94d560557d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Industrial AI &amp; Data Engineer (H/F)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Vicat</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Kafka, Hadoop, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef46044606bc80da</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Prompt Engineering, S3, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fedf9e582c7c5a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Google Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7ff7bbafc6e541</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Databricks, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=159c1652cc5c9d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5377d18b526114a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, FastAPI, Kubernetes, CI/CD, Jenkins, MySQL, MongoDB</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, PySpark</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, CI/CD, Git, Snowflake, Redshift, PostgreSQL, Python, SQL, R</t>
+          <t>Gemini, S3, Glue, Athena, Redshift, Docker, Kubernetes, CI/CD, Git, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Operations Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f692b1dac1269e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Senior Generative AI Developer (LLMs | AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, S3, Docker, Kubernetes, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e602d2e400325ba0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,1337 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=647c0383e2507f57</t>
+          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a32220aba8f0ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8fa389489d6484c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd4355566db11649</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Enterprise Data Scientist - Patient Experience</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CHS Corporate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, Keras, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d24b4b24f57e67</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6ff07390148e9c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da59d341b834c758</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Skillproof</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=280c14cac1c4c2c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>USAA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a14b7adb6865b6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Java AI / ML Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>11.1</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5377d18b526114a</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Synapse, Data Lake, Snowflake, Power BI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, BigQuery, FastAPI, Kubernetes, BigQuery, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77b168d1693e53a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Cloud IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (Teradyne, North Reading)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Teradyne</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>North Reading, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, Gemini, Copilot, Hugging Face, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8c2996aa01eb16e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BAE Systems USA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>York, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b63db783bb0ec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Afresh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e4da7774c161538</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c3f481b54f8f606</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Prompt Engineering, S3, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44fca4b98ce5c16b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4df35ddb9b7c9ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a20cd5e629173a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, Docker, Terraform, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cfc1b0d9e916b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80245f5ff0827422</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9b3a4f5a5cf2a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d11cba8e49f2cd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b108729553113c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Applied AI, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Savvy Wealth</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f3326a2b788d3eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Founding Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Savvy Wealth</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d0d50aaeea60243</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer - Back End</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Churchill Downs Inc.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da1aa453aa9691ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer - Back End</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Churchill Downs Inc.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d45cdd6285fa1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>First Primary Care</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Copilot, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=356a853fb429eed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EIS Group</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, XGBoost, S3, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acd3daa5b4b6bd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Databricks, Python, SQL, R, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b0f598c7174f08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Healthcare Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PostgreSQL, Tableau, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d28547a5f6a95215</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lake, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI) Intern</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aae5e3a7ea4ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI) Intern</t>
+          <t>Sr. Gen AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f43077146e6a6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f99f12ea8fa755d0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior network engineer</t>
+          <t>Senior Generative AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b6422803f19eda</t>
+          <t>https://www.indeed.com/viewjob?jk=f34bdaca0c37db3c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, Hugging Face, TensorFlow, PyTorch, Docker, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>AI Engineer, RAG, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist/Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maynard, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Docker</t>
+          <t>Generative AI, Hugging Face, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2583eb7edcc76e</t>
+          <t>https://www.indeed.com/viewjob?jk=224bb926896af553</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Seaborn</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Azure ML, Data Lake, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=68962437d33fb2d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,229 +776,229 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Infrastructure Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>EyeQ Monitoring</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Copilot, S3, EC2, Kubernetes, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f74565a38f0979</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4fa5902e86d18f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer [Chicago Only]</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8th Light</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cd65c9619effdc</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Birdeye</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Snowflake, Kafka, Hadoop, Python, R, Scala</t>
+          <t>Data Scientist, Prompt Engineering, spaCy, NLTK, Gensim, FastAPI, Docker, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9928be508cf14a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer IV - Operations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Autonomous Solutions</t>
+          <t>Birdeye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Logan, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Prompt Engineering, spaCy, NLTK, Gensim, FastAPI, Docker, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9ecfffe8ad1dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee1b1dc99f75c4c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Consumers Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Git, Databricks, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c145f55cb53306</t>
+          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Science Senior Advisors- Hybrid</t>
+          <t>Senior .NET Software Engineer - Vilnius, Lithuania</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd8d915be1b91e</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b2a94d0527a6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Data Annotator</t>
+          <t>Senior Software Engineer - Vilnius, Lithuania</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ardor IT Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,91 +1007,546 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, FastAPI, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b48f1316feb42a</t>
+          <t>https://www.indeed.com/viewjob?jk=04feafbb1d6987db</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor - Evernorth</t>
+          <t>Jr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Astiva Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, FastAPI, Docker, CI/CD, Git, Python, R</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, AWS SageMaker, Azure ML, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf217d3970b6ddca</t>
+          <t>https://www.indeed.com/viewjob?jk=2166896d6d58fe36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor - Evernorth</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Agentic)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CloudBees Inc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lewes, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, Gemini, Prompt Engineering, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d31a72c28d05769</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>softech inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f69cb739f834973</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Streaming</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CRUSOE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=925c29a40e8b5eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FujiFilm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI Defense Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WilmerHale</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72a4116c9e0aaa7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Applied AI, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Savvy Wealth</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, FastAPI, Docker, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cba5c6ebf57df2b5</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0443c6397cc44a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Founding Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Savvy Wealth</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d905a381141a6548</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Test Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae828a5b170f5cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Birdeye</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dd504ad6a294180</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AGMEDNET Inc</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19939067ba7116af</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Specialist -Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bfa4d7e8f06157d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Breckenridge Grand Vacations</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Breckenridge, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c6e381ef288041a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-10.xlsx
+++ b/daily_matches/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - Software Engineering</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Synapse, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, Keras, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
+          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Gen AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99f12ea8fa755d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Generative AI Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34bdaca0c37db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Sr. Generative AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Geopaq Logic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8c0a3b4cc4061c26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Hugging Face, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Gemini, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224bb926896af553</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>AWS Java Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CleanSlate Technology Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Azure ML, Data Lake, Git, Databricks</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, CI/CD, Terraform, Git, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68962437d33fb2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a24b1c6ccb2c07f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, PyTorch, Keras, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Data Scientist Commercial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, MLflow, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5257eb372c667aae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0f59b3d330f09703</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EyeQ Monitoring</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,752 +801,367 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Kubernetes, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4fa5902e86d18f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd69006bae592dc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Hugging Face, TensorFlow, PyTorch, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=1a60db6f8cc2a432</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Birdeye</t>
+          <t>VueData Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, spaCy, NLTK, Gensim, FastAPI, Docker, Git, NoSQL, Python</t>
+          <t>RAG, Pinecone, Docker, CI/CD, Kafka, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9928be508cf14a</t>
+          <t>https://www.indeed.com/viewjob?jk=87dee35e3cc808de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Birdeye</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, spaCy, NLTK, Gensim, FastAPI, Docker, Git, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Jenkins, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee1b1dc99f75c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=19ef0d446071ac61</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
+          <t>Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2a73a6451d2683</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior .NET Software Engineer - Vilnius, Lithuania</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Jenkins, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b2a94d0527a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d668b8e103c1b53d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vilnius, Lithuania</t>
+          <t>AI Data Scientist Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04feafbb1d6987db</t>
+          <t>https://www.indeed.com/viewjob?jk=05a9681d2a333ac4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jr. AI/ML Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Astiva Health</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, AWS SageMaker, Azure ML, Python, R</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2166896d6d58fe36</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>MES Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
+          <t>Git, MySQL, MongoDB, Tableau, Quicksight, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=87824637ed2df06b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Agentic)</t>
+          <t>Fullstack Machine Learning Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lewes, DE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Gemini, Prompt Engineering, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d31a72c28d05769</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c4a7ae52e4bf8b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>softech inc</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f69cb739f834973</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Streaming</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CRUSOE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Kinesis, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=925c29a40e8b5eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FujiFilm</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior AI Defense Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>WilmerHale</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72a4116c9e0aaa7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Applied AI, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Savvy Wealth</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0443c6397cc44a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Founding Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Savvy Wealth</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d905a381141a6548</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Test Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae828a5b170f5cdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Birdeye</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd504ad6a294180</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>AGMEDNET Inc</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19939067ba7116af</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Specialist -Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfa4d7e8f06157d</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Breckenridge Grand Vacations</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Breckenridge, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6e381ef288041a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5f038b0ab7a88</t>
         </is>
       </c>
     </row>
